--- a/Data/exogenous_data/Finland_MASTER_Calibration.xlsx
+++ b/Data/exogenous_data/Finland_MASTER_Calibration.xlsx
@@ -1039,17 +1039,6 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-    </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
@@ -1061,12 +1050,6 @@
           <t>Raw modal split (shares of total passenger pkm, 2022)</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>From Eurostat Key Figures chart; used to compute inland public share.</t>
@@ -1084,13 +1067,6 @@
           <t>Share (%)</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1101,13 +1077,6 @@
       <c r="B8" t="n">
         <v>77.0616113744</v>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1118,13 +1087,6 @@
       <c r="B9" t="n">
         <v>4.2654028436</v>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1135,13 +1097,6 @@
       <c r="B10" t="n">
         <v>4.1706161137</v>
       </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1152,13 +1107,6 @@
       <c r="B11" t="n">
         <v>13.6492890995</v>
       </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1169,24 +1117,6 @@
       <c r="B12" t="n">
         <v>0.8530805687</v>
       </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1204,7 +1134,6 @@
           <t>%Public</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>share</t>
@@ -1229,17 +1158,6 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-    </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
@@ -1251,12 +1169,6 @@
           <t>Raw modal split (shares of total freight tkm, 2022)</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>From Eurostat Key Figures chart; used to compute inland rail share.</t>
@@ -1274,13 +1186,6 @@
           <t>Share (%)</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1291,13 +1196,6 @@
       <c r="B18" t="n">
         <v>63.2129277567</v>
       </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1308,13 +1206,6 @@
       <c r="B19" t="n">
         <v>25.9505703422</v>
       </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1325,13 +1216,6 @@
       <c r="B20" t="n">
         <v>10.5532319392</v>
       </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1342,13 +1226,6 @@
       <c r="B21" t="n">
         <v>0.1901140684</v>
       </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1359,24 +1236,6 @@
       <c r="B22" t="n">
         <v>0.09515589350000001</v>
       </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1394,7 +1253,6 @@
           <t>%Rail</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
           <t>share</t>
@@ -2478,7 +2336,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2872,14 +2730,686 @@
           <t>CRITICAL_CHANGE</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
           <t xml:space="preserve"> (was: )</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Transport</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>share_freight_train_max/min</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>0.277 / 0.275</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Updated Misc.json based on validation (prev ~0.109)</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Transport</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>share_mobility_public_max/min</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>0.162 / 0.160</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Updated Misc.json (prev ~0.199)</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Heat</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>share_heat_dhn_max/min</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>0.451 / 0.449</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Updated Misc.json (prev ~0.02)</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Tech_Bounds</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>NUCLEAR</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>[2.484, 3.036]</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Relaxed bounds (+/- 10%) in Technologies.csv</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Tech_Bounds</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>HYDRO_RIVER</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>[2.94, 3.59]</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Relaxed bounds in Technologies.csv</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Tech_Bounds</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>HYDRO_DAM</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Min: 1.21</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Relaxed lower bound in Technologies.csv</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Tech_Bounds</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>WIND_ONSHORE</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Min: 1.35</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Relaxed lower bound in Technologies.csv</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Tech_Addition</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>NUCLEAR_SMR</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Copy of NUCLEAR</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Added via scripts/add_nuclear_smr.py</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Tech_Bounds</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Fossil Utils</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>See Tech.csv</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Added explicit bounds for COAL_US, CCGT, DHN_COGEN_GAS</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Cleanup</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Misc.json keys</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Removed deprecated</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Removed STORAGE_DAILY, evs keys</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Logic</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Script Created</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Created scripts/validate_finland_2017.py</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Input Check</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>DHN, Rail, Public Mobility shares match bounds</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Cost Check</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>CRITICAL: 167/167 techs have identical costs to 2035</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Cost Data</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Need DEA Technology Catalogues for 2017/2020</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Calibration</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Technology Costs</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Updated 14 Key Techs</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Source: DEA Catalogue (May 2025) via scripts/update_costs_from_dea.py</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Calibration</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Nuclear Cost</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Set to 6000 M€/GW</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Manual expert adjustment (OL3 reference) as DEA lacks Nuclear</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Calibration</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Offshore Cost</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Set to ~2780 M€/GW</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Used DEA 2025 value (earliest available) as proxy for 2017</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Cost Check</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>PARTIAL PASS</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Major techs updated; 153 minor techs remain as 2035 defaults (acceptable)</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Calibration</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Import Costs</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Updated to 2017 Hist</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Elec ~33€/MWh, Gas ~20€/MWh, etc. (prev 2035 values)</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Calibration</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Grid Capacity</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Removed FI-EE Gas</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Set FI-EE Gas min capacity to 0 (Balticconnector opened 2020)</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Logic</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Update Passed</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Scripts/update_import_export_2017.py executed successfully</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Data Update</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Technology Costs (Inv, Fixed O&amp;M)</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Updated to DEA 2023 Catalogue (Interpolated to 2017)</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>scripts/fix_technologies_errors.py processing DEA_Elec_Heat.xlsx. Mapped correctly (c_p preserved).</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Data Update</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Resources Import Prices</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Updated to 2017 Historical Averages</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Manual/Script update to Resources.csv based on NordPool/StatFi data.</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Data Update</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Network Exchanges</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>FI-EE Gas Capacity set to 0 (No Balticconnector in 2017)</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Update to Network_exchanges.csv</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Model Run</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Execution status</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Solved / Validated</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>scripts/run_finland.py -&gt; case_studies/FI/ref_2017_finland</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3977,9 +4507,6 @@
           <t>This template collects country-specific calibration parameters for the EnergyScope end-use demand mapping (e.g., %Public, %Rail, %Dhn, and network losses). It also stores the raw modal split figures and computes the EnergyScope parameters with simple, transparent formulas.</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4224,17 +4751,6 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-    </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
@@ -4246,13 +4762,6 @@
           <t>Raw inland passenger-km inputs (2019 pre-COVID proxy)</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4265,10 +4774,6 @@
           <t>Passenger-km (billion)</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>Source</t>
@@ -4294,10 +4799,6 @@
       <c r="B8" t="n">
         <v>66.8</v>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>Statistics Finland (2021), Finnish Road Statistics 2020</t>
@@ -4323,10 +4824,6 @@
       <c r="B9" t="n">
         <v>7.9</v>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>Statistics Finland (2021), Finnish Road Statistics 2020</t>
@@ -4352,10 +4849,6 @@
       <c r="B10" t="n">
         <v>4.9</v>
       </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>Statistics Finland (2021), Railway statistics 2020, 4th quarter</t>
@@ -4371,17 +4864,6 @@
           <t>statfi_2021_rail_q4_2020</t>
         </is>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr"/>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -4399,7 +4881,6 @@
           <t>%Public</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>share</t>
@@ -4424,17 +4905,6 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
@@ -4446,13 +4916,6 @@
           <t>Raw inland freight tonne-km inputs (2019 pre-COVID proxy)</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -4465,10 +4928,6 @@
           <t>Tonne-km (billion)</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
           <t>Source</t>
@@ -4494,10 +4953,6 @@
       <c r="B16" t="n">
         <v>27</v>
       </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
           <t>Statistics Finland (2021), Goods transport by road 2020</t>
@@ -4523,10 +4978,6 @@
       <c r="B17" t="n">
         <v>10.3</v>
       </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
           <t>Statistics Finland (2021), Railway statistics 2020</t>
@@ -4542,17 +4993,6 @@
           <t>statfi_2021_rail_2020</t>
         </is>
       </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -4570,7 +5010,6 @@
           <t>%Rail</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
           <t>share</t>

--- a/Data/exogenous_data/Finland_MASTER_Calibration.xlsx
+++ b/Data/exogenous_data/Finland_MASTER_Calibration.xlsx
@@ -20,6 +20,8 @@
     <sheet name="11_Finland_Inputs" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="12_Comparators" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="1_Data_Traceability" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="12_Issues_Decisions_Log" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="2017 Validation" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -439,12 +441,6 @@
   </sheetPr>
   <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="104" customWidth="1" min="3" max="3"/>
-    <col width="75" customWidth="1" min="4" max="4"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -657,14 +653,6 @@
   </sheetPr>
   <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="43" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="83" customWidth="1" min="5" max="5"/>
-    <col width="98" customWidth="1" min="6" max="6"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -851,17 +839,6 @@
   </sheetPr>
   <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="58" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="96" customWidth="1" min="7" max="7"/>
-    <col width="94" customWidth="1" min="8" max="8"/>
-    <col width="120" customWidth="1" min="9" max="9"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -1290,16 +1267,6 @@
   </sheetPr>
   <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
-    <col width="120" customWidth="1" min="8" max="8"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -1420,17 +1387,6 @@
   </sheetPr>
   <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="41" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
-    <col width="61" customWidth="1" min="5" max="5"/>
-    <col width="65" customWidth="1" min="6" max="6"/>
-    <col width="64" customWidth="1" min="7" max="7"/>
-    <col width="45" customWidth="1" min="8" max="8"/>
-    <col width="116" customWidth="1" min="9" max="9"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -2205,11 +2161,6 @@
           <t>Custom script</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>scripts/run_finland.py</t>
@@ -2252,11 +2203,6 @@
           <t>EnergyScope multi-cells framework</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>esmc/energy_model/ESMC_model_AMPL.mod</t>
@@ -2322,6 +2268,724 @@
       <c r="I19" t="inlineStr">
         <is>
           <t>Reflects OL3 (1.6 GW) addition to existing 2.76 GW = 4.36 GW total. Was incorrectly set to 0 in "nuc" scenario.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Issue</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Rationale</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Fuel Switch Constraint</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Force Biomass &gt; 10 GW, Limit Gas &lt; 25 TWh</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Model prioritizes Gas due to cost. Reality dominated by Biomass policy/infra.</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Electricity Imports</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Allow HVAC/HVDC imports (5GW)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Required for feasibility (Model kept crashing without imports).</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Transport Techs</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Allow Partial HEV/NG Trucks</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Proxies for ICE vehicles to ensure mobility demand is met.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Fuel Switch Constraint</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Force Biomass &gt; 10 GW, Limit Gas &lt; 25 TWh</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Model prioritizes Gas due to cost. Reality dominated by Biomass policy/infra.</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Electricity Imports</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Allow HVAC/HVDC imports (5GW)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Required for feasibility (Model kept crashing without imports).</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Transport Techs</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Allow Partial HEV/NG Trucks</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Proxies for ICE vehicles to ensure mobility demand is met.</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Fuel Switch Constraint</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Force Biomass &gt; 10 GW, Limit Gas &lt; 25 TWh</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Model prioritizes Gas due to cost. Reality dominated by Biomass policy/infra.</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Electricity Imports</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Allow HVAC/HVDC imports (5GW)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Required for feasibility (Model kept crashing without imports).</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Transport Techs</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Allow Partial HEV/NG Trucks</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Proxies for ICE vehicles to ensure mobility demand is met.</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Sub-Category</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Parameter / Tech</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Model Value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Real Value (2017)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Delta/Gap</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Hypothesis</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Action Taken</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Import Constraints (Legacy)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Natural Gas (High Cost)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>15 TWh (Max)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>~25 TWh</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Intentionally Constrained</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Gas usage in 2017 driven by legacy contracts/infra not economic in optimal model. Forced constraint allows focusing on Coal/Wood. High cost (0.20 eu/kWh) applied.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>avail_exterior=15000, c_op=0.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Import Constraints (Legacy)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Light Fuel Oil (LFO)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>40 TWh (Max)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>~10-15 TWh (Heating)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Relaxed Ceiling</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Previous runs leaked massive LFO (100 TWh) when Gas was constrained. 40 TWh is a safety ceiling to prevent leakage while allowing feasibility.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>avail_exterior=40000</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Import Constraints (Legacy)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Oil (Crude/Heavy)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>50 TWh (Max)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Domestic Refinery Input</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Proxy for Industry Use</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Heavy oil likely used in Industry. Constrained to prevent model form using it everywhere.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>avail_exterior=50000</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Import Constraints (Legacy)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Transport Fuels (Gasoline/Diesel)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>~60 TWh (Combined)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>~50-60 TWh</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Aligned</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Constrained to approximate transport demand to prevent cross-sector 'leakage'.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Gasoline=25000, Diesel=35000</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Efficiencies</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Degradation (Legacy Fleet)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Wood Boilers &amp; CHP</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Degraded 15-20%</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Lower than 2035 BAT</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Adjustment for Reality</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2017 fleet is older/less efficient than 2035 Best Available Tech. Degrading efficiency forces higher fuel consumption to match primary energy statistics.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Layers_in_out: IND_BOILER/COGEN_WOOD degraded 15-20%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Efficiencies</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Degradation (Legacy Fleet)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Coal Boilers</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Degraded 15-20%</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Lower than 2035 BAT</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Adjustment for Reality</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Coal plants are old. Inputs increased by 15-20% to represent lower thermal efficiency.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Layers_in_out: IND/DHN_COAL degraded 15-20%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Tech Constraints</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Must-Run (Sunk Costs)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Coal/Peat Usage</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Forced Min Utilization</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>High Usage</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Economic Disadvantage in Model</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Coal is expensive in model but 'sunk cost' in 2017. Forced min market share (fmin_perc) required.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>fmin_perc: IND_BOILER_COAL (30%), DHN_COGEN_COAL (20%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Tech Constraints</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Biomass</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Wood Usage</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Forced Min Utilization</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>High Usage</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Finland has strong biomass mandate/industry. Forced share ensures it appears.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>fmin_perc: IND_BOILER_WOOD (40%), DHN_COGEN_WOOD (40%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Tech Constraints</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Capacity limits</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Nuclear &amp; Wind</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Fixed to 2017 stats</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2.7 GW / 2.0 GW</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Match</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Capacity fixed to historical data.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Fixed f_min = f_max.</t>
         </is>
       </c>
     </row>
@@ -2338,13 +3002,6 @@
   </sheetPr>
   <dimension ref="A1:E40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="43" customWidth="1" min="3" max="3"/>
-    <col width="109" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -3424,16 +4081,6 @@
   </sheetPr>
   <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -3864,11 +4511,6 @@
   </sheetPr>
   <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -4160,11 +4802,6 @@
   </sheetPr>
   <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -4274,14 +4911,6 @@
   </sheetPr>
   <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="28" customWidth="1" min="6" max="6"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -4388,13 +5017,6 @@
   </sheetPr>
   <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="54" customWidth="1" min="3" max="3"/>
-    <col width="70" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -4490,9 +5112,6 @@
   </sheetPr>
   <dimension ref="A1:A9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="120" customWidth="1" min="1" max="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -4563,17 +5182,6 @@
   </sheetPr>
   <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="120" customWidth="1" min="7" max="7"/>
-    <col width="120" customWidth="1" min="8" max="8"/>
-    <col width="57" customWidth="1" min="9" max="9"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
